--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/StructureDefinition/onc-abbey-pain-scale</t>
+    <t>https://opennursingcoreig.com/StructureDefinition/onc-abbey-pain-scale</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4394" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4394" uniqueCount="567">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,14 +617,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="exam"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes for high level observation categories.</t>
@@ -3924,7 +3916,7 @@
         <v>18</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>18</v>
@@ -3942,23 +3934,23 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3985,10 +3977,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3996,13 +3988,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>18</v>
@@ -4046,7 +4038,7 @@
         <v>18</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>18</v>
@@ -4064,10 +4056,10 @@
         <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -4109,10 +4101,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -4120,14 +4112,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4149,16 +4141,16 @@
         <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -4168,29 +4160,29 @@
         <v>18</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
@@ -4207,7 +4199,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4222,30 +4214,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4268,19 +4260,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -4329,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4344,19 +4336,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -4364,10 +4356,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4390,16 +4382,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4449,7 +4441,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4470,13 +4462,13 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4484,14 +4476,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4510,19 +4502,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4571,7 +4563,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4586,19 +4578,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4606,14 +4598,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4632,19 +4624,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4693,7 +4685,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4708,19 +4700,19 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4728,10 +4720,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4754,16 +4746,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4813,7 +4805,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4834,13 +4826,13 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4848,10 +4840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4874,17 +4866,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4933,7 +4925,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4948,19 +4940,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4968,10 +4960,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4994,19 +4986,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -5055,7 +5047,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5064,7 +5056,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -5073,27 +5065,27 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5116,13 +5108,13 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5173,7 +5165,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5197,7 +5189,7 @@
         <v>18</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>18</v>
@@ -5208,10 +5200,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5240,7 +5232,7 @@
         <v>137</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>139</v>
@@ -5281,19 +5273,19 @@
         <v>18</v>
       </c>
       <c r="AB26" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AC26" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AC26" t="s" s="2">
+      <c r="AD26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5317,7 +5309,7 @@
         <v>18</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>18</v>
@@ -5328,10 +5320,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5354,19 +5346,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5415,7 +5407,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5436,10 +5428,10 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
@@ -5450,10 +5442,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5479,20 +5471,20 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="P28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q28" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="P28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q28" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="R28" t="s" s="2">
         <v>18</v>
@@ -5516,28 +5508,28 @@
         <v>179</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5558,10 +5550,10 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>18</v>
@@ -5572,10 +5564,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5598,17 +5590,17 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5618,46 +5610,46 @@
         <v>18</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5678,10 +5670,10 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
@@ -5692,10 +5684,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5721,14 +5713,14 @@
         <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>18</v>
@@ -5738,46 +5730,46 @@
         <v>18</v>
       </c>
       <c r="S30" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5786,7 +5778,7 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5798,10 +5790,10 @@
         <v>18</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>18</v>
@@ -5812,10 +5804,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5841,16 +5833,16 @@
         <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -5899,7 +5891,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5920,10 +5912,10 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>18</v>
@@ -5934,10 +5926,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5963,16 +5955,16 @@
         <v>188</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5997,14 +5989,14 @@
         <v>18</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y32" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="Z32" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>18</v>
       </c>
@@ -6021,7 +6013,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6030,7 +6022,7 @@
         <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>102</v>
@@ -6045,7 +6037,7 @@
         <v>133</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -6056,14 +6048,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6085,16 +6077,16 @@
         <v>188</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -6119,14 +6111,14 @@
         <v>18</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>18</v>
       </c>
@@ -6143,7 +6135,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6161,27 +6153,27 @@
         <v>18</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6204,19 +6196,19 @@
         <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>18</v>
@@ -6265,7 +6257,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6286,10 +6278,10 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -6300,10 +6292,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6329,13 +6321,13 @@
         <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6361,14 +6353,14 @@
         <v>18</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>18</v>
       </c>
@@ -6385,7 +6377,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6403,27 +6395,27 @@
         <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>377</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6449,16 +6441,16 @@
         <v>188</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
@@ -6483,14 +6475,14 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
       </c>
@@ -6507,7 +6499,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6528,10 +6520,10 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
@@ -6542,10 +6534,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6568,16 +6560,16 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6627,7 +6619,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6645,27 +6637,27 @@
         <v>18</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6688,16 +6680,16 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6747,7 +6739,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6765,27 +6757,27 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6808,19 +6800,19 @@
         <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6869,7 +6861,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6881,19 +6873,19 @@
         <v>18</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AK39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6904,10 +6896,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6930,13 +6922,13 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6987,7 +6979,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7011,7 +7003,7 @@
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -7022,10 +7014,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7054,7 +7046,7 @@
         <v>137</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>139</v>
@@ -7107,7 +7099,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7131,7 +7123,7 @@
         <v>18</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -7142,14 +7134,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7171,10 +7163,10 @@
         <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>139</v>
@@ -7229,7 +7221,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7264,10 +7256,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7290,13 +7282,13 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7347,7 +7339,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7356,7 +7348,7 @@
         <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>102</v>
@@ -7368,10 +7360,10 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -7382,10 +7374,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7408,13 +7400,13 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7465,7 +7457,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7474,7 +7466,7 @@
         <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>102</v>
@@ -7486,10 +7478,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7500,10 +7492,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7529,16 +7521,16 @@
         <v>188</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>18</v>
@@ -7566,11 +7558,11 @@
         <v>114</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>18</v>
       </c>
@@ -7587,7 +7579,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7605,13 +7597,13 @@
         <v>18</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AN45" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7622,10 +7614,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7651,16 +7643,16 @@
         <v>188</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>18</v>
@@ -7685,14 +7677,14 @@
         <v>18</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7709,7 +7701,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7727,13 +7719,13 @@
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AN46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7744,10 +7736,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7770,17 +7762,17 @@
         <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7829,7 +7821,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7853,7 +7845,7 @@
         <v>18</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>18</v>
@@ -7864,10 +7856,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7890,13 +7882,13 @@
         <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7947,7 +7939,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7968,10 +7960,10 @@
         <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>18</v>
@@ -7982,10 +7974,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8008,16 +8000,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8067,7 +8059,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8088,10 +8080,10 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>18</v>
@@ -8102,10 +8094,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8128,16 +8120,16 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8187,7 +8179,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8208,10 +8200,10 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -8222,10 +8214,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8248,19 +8240,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -8297,17 +8289,17 @@
         <v>18</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8328,10 +8320,10 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>18</v>
@@ -8342,10 +8334,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8368,13 +8360,13 @@
         <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8425,7 +8417,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8449,7 +8441,7 @@
         <v>18</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
@@ -8460,10 +8452,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8492,7 +8484,7 @@
         <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -8545,7 +8537,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8569,7 +8561,7 @@
         <v>18</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -8580,14 +8572,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8609,10 +8601,10 @@
         <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>139</v>
@@ -8667,7 +8659,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8702,10 +8694,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8731,16 +8723,16 @@
         <v>188</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N55" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O55" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>18</v>
@@ -8765,14 +8757,14 @@
         <v>18</v>
       </c>
       <c r="X55" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y55" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y55" t="s" s="2">
+      <c r="Z55" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>18</v>
       </c>
@@ -8789,7 +8781,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8807,16 +8799,16 @@
         <v>18</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>18</v>
@@ -8824,10 +8816,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8850,19 +8842,19 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O56" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8911,7 +8903,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8929,27 +8921,27 @@
         <v>18</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8975,16 +8967,16 @@
         <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N57" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -9009,14 +9001,14 @@
         <v>18</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
       </c>
@@ -9033,7 +9025,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9042,7 +9034,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -9057,7 +9049,7 @@
         <v>133</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>18</v>
@@ -9068,14 +9060,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9097,16 +9089,16 @@
         <v>188</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -9131,14 +9123,14 @@
         <v>18</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>18</v>
       </c>
@@ -9155,7 +9147,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9173,27 +9165,27 @@
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9219,16 +9211,16 @@
         <v>80</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N59" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9277,7 +9269,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9298,10 +9290,10 @@
         <v>18</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9312,13 +9304,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>18</v>
@@ -9340,19 +9332,19 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -9401,7 +9393,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9422,10 +9414,10 @@
         <v>18</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>18</v>
@@ -9436,10 +9428,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9462,13 +9454,13 @@
         <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9519,7 +9511,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9543,7 +9535,7 @@
         <v>18</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9554,10 +9546,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9586,7 +9578,7 @@
         <v>137</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>139</v>
@@ -9639,7 +9631,7 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9663,7 +9655,7 @@
         <v>18</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9674,14 +9666,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9703,10 +9695,10 @@
         <v>136</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>139</v>
@@ -9761,7 +9753,7 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9796,10 +9788,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9825,16 +9817,16 @@
         <v>188</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O64" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>18</v>
@@ -9844,7 +9836,7 @@
         <v>18</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>18</v>
@@ -9859,14 +9851,14 @@
         <v>18</v>
       </c>
       <c r="X64" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y64" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y64" t="s" s="2">
+      <c r="Z64" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>18</v>
       </c>
@@ -9883,7 +9875,7 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>90</v>
@@ -9901,16 +9893,16 @@
         <v>18</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>18</v>
@@ -9918,10 +9910,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9944,19 +9936,19 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>509</v>
-      </c>
       <c r="M65" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>18</v>
@@ -10005,7 +9997,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10023,27 +10015,27 @@
         <v>18</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10069,16 +10061,16 @@
         <v>188</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N66" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O66" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -10103,14 +10095,14 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y66" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y66" t="s" s="2">
+      <c r="Z66" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
       </c>
@@ -10127,7 +10119,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10136,7 +10128,7 @@
         <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>102</v>
@@ -10151,7 +10143,7 @@
         <v>133</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>18</v>
@@ -10162,14 +10154,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10191,16 +10183,16 @@
         <v>188</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
@@ -10225,14 +10217,14 @@
         <v>18</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>18</v>
       </c>
@@ -10249,7 +10241,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10267,27 +10259,27 @@
         <v>18</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10313,16 +10305,16 @@
         <v>80</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N68" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O68" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>18</v>
@@ -10371,7 +10363,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10392,10 +10384,10 @@
         <v>18</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>18</v>
@@ -10406,13 +10398,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>18</v>
@@ -10434,19 +10426,19 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>18</v>
@@ -10495,7 +10487,7 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10516,10 +10508,10 @@
         <v>18</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>18</v>
@@ -10530,10 +10522,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10556,13 +10548,13 @@
         <v>18</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10613,7 +10605,7 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10637,7 +10629,7 @@
         <v>18</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>18</v>
@@ -10648,10 +10640,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10680,7 +10672,7 @@
         <v>137</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>139</v>
@@ -10733,7 +10725,7 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10757,7 +10749,7 @@
         <v>18</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>18</v>
@@ -10768,14 +10760,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10797,10 +10789,10 @@
         <v>136</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>139</v>
@@ -10855,7 +10847,7 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10890,10 +10882,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10919,16 +10911,16 @@
         <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N73" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O73" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>18</v>
@@ -10938,7 +10930,7 @@
         <v>18</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>18</v>
@@ -10953,14 +10945,14 @@
         <v>18</v>
       </c>
       <c r="X73" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y73" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y73" t="s" s="2">
+      <c r="Z73" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>18</v>
       </c>
@@ -10977,7 +10969,7 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>90</v>
@@ -10995,16 +10987,16 @@
         <v>18</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AO73" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>18</v>
@@ -11012,10 +11004,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11038,19 +11030,19 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M74" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O74" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>18</v>
@@ -11099,7 +11091,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11117,27 +11109,27 @@
         <v>18</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11163,16 +11155,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N75" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>18</v>
@@ -11197,14 +11189,14 @@
         <v>18</v>
       </c>
       <c r="X75" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y75" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y75" t="s" s="2">
+      <c r="Z75" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>18</v>
       </c>
@@ -11221,7 +11213,7 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11230,7 +11222,7 @@
         <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>102</v>
@@ -11245,7 +11237,7 @@
         <v>133</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>18</v>
@@ -11256,14 +11248,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11285,16 +11277,16 @@
         <v>188</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>18</v>
@@ -11319,14 +11311,14 @@
         <v>18</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>18</v>
       </c>
@@ -11343,7 +11335,7 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11361,27 +11353,27 @@
         <v>18</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11407,16 +11399,16 @@
         <v>80</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N77" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>18</v>
@@ -11465,7 +11457,7 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11486,10 +11478,10 @@
         <v>18</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>18</v>
@@ -11500,13 +11492,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>18</v>
@@ -11528,19 +11520,19 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>18</v>
@@ -11589,7 +11581,7 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11610,10 +11602,10 @@
         <v>18</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>18</v>
@@ -11624,10 +11616,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11650,13 +11642,13 @@
         <v>18</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11707,7 +11699,7 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11731,7 +11723,7 @@
         <v>18</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>18</v>
@@ -11742,10 +11734,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11774,7 +11766,7 @@
         <v>137</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>139</v>
@@ -11827,7 +11819,7 @@
         <v>18</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11851,7 +11843,7 @@
         <v>18</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>18</v>
@@ -11862,14 +11854,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11891,10 +11883,10 @@
         <v>136</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>139</v>
@@ -11949,7 +11941,7 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11984,10 +11976,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12013,16 +12005,16 @@
         <v>188</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N82" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O82" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>18</v>
@@ -12032,7 +12024,7 @@
         <v>18</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>18</v>
@@ -12047,14 +12039,14 @@
         <v>18</v>
       </c>
       <c r="X82" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y82" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y82" t="s" s="2">
+      <c r="Z82" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z82" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA82" t="s" s="2">
         <v>18</v>
       </c>
@@ -12071,7 +12063,7 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -12089,16 +12081,16 @@
         <v>18</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>18</v>
@@ -12106,10 +12098,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12132,19 +12124,19 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O83" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>18</v>
@@ -12193,7 +12185,7 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12211,27 +12203,27 @@
         <v>18</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12257,16 +12249,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N84" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>18</v>
@@ -12291,14 +12283,14 @@
         <v>18</v>
       </c>
       <c r="X84" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y84" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y84" t="s" s="2">
+      <c r="Z84" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>18</v>
       </c>
@@ -12315,7 +12307,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12324,7 +12316,7 @@
         <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>102</v>
@@ -12339,7 +12331,7 @@
         <v>133</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>18</v>
@@ -12350,14 +12342,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12379,16 +12371,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>18</v>
@@ -12413,14 +12405,14 @@
         <v>18</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>18</v>
       </c>
@@ -12437,7 +12429,7 @@
         <v>18</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12455,27 +12447,27 @@
         <v>18</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12501,16 +12493,16 @@
         <v>80</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N86" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O86" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>18</v>
@@ -12559,7 +12551,7 @@
         <v>18</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12580,10 +12572,10 @@
         <v>18</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>18</v>
@@ -12594,13 +12586,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C87" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>18</v>
@@ -12622,19 +12614,19 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>18</v>
@@ -12683,7 +12675,7 @@
         <v>18</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12704,10 +12696,10 @@
         <v>18</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>18</v>
@@ -12718,10 +12710,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12744,13 +12736,13 @@
         <v>18</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12801,7 +12793,7 @@
         <v>18</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12825,7 +12817,7 @@
         <v>18</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>18</v>
@@ -12836,10 +12828,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12868,7 +12860,7 @@
         <v>137</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>139</v>
@@ -12921,7 +12913,7 @@
         <v>18</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12945,7 +12937,7 @@
         <v>18</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>18</v>
@@ -12956,14 +12948,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12985,10 +12977,10 @@
         <v>136</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>139</v>
@@ -13043,7 +13035,7 @@
         <v>18</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13078,10 +13070,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13107,16 +13099,16 @@
         <v>188</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N91" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>18</v>
@@ -13126,7 +13118,7 @@
         <v>18</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>18</v>
@@ -13141,14 +13133,14 @@
         <v>18</v>
       </c>
       <c r="X91" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y91" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y91" t="s" s="2">
+      <c r="Z91" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>18</v>
       </c>
@@ -13165,7 +13157,7 @@
         <v>18</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>90</v>
@@ -13183,16 +13175,16 @@
         <v>18</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>18</v>
@@ -13200,10 +13192,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13226,19 +13218,19 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O92" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>18</v>
@@ -13287,7 +13279,7 @@
         <v>18</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13305,27 +13297,27 @@
         <v>18</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13351,16 +13343,16 @@
         <v>188</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N93" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>18</v>
@@ -13385,14 +13377,14 @@
         <v>18</v>
       </c>
       <c r="X93" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y93" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y93" t="s" s="2">
+      <c r="Z93" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>18</v>
       </c>
@@ -13409,7 +13401,7 @@
         <v>18</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13418,7 +13410,7 @@
         <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>102</v>
@@ -13433,7 +13425,7 @@
         <v>133</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>18</v>
@@ -13444,14 +13436,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13473,16 +13465,16 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>18</v>
@@ -13507,14 +13499,14 @@
         <v>18</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>18</v>
       </c>
@@ -13531,7 +13523,7 @@
         <v>18</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13549,27 +13541,27 @@
         <v>18</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13595,16 +13587,16 @@
         <v>80</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M95" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N95" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>18</v>
@@ -13653,7 +13645,7 @@
         <v>18</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13674,10 +13666,10 @@
         <v>18</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>18</v>
@@ -13688,13 +13680,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>18</v>
@@ -13716,19 +13708,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>18</v>
@@ -13777,7 +13769,7 @@
         <v>18</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13798,10 +13790,10 @@
         <v>18</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>18</v>
@@ -13812,10 +13804,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13838,13 +13830,13 @@
         <v>18</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13895,7 +13887,7 @@
         <v>18</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13919,7 +13911,7 @@
         <v>18</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>18</v>
@@ -13930,10 +13922,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13962,7 +13954,7 @@
         <v>137</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>139</v>
@@ -14015,7 +14007,7 @@
         <v>18</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14039,7 +14031,7 @@
         <v>18</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>18</v>
@@ -14050,14 +14042,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14079,10 +14071,10 @@
         <v>136</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>139</v>
@@ -14137,7 +14129,7 @@
         <v>18</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14172,10 +14164,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14201,16 +14193,16 @@
         <v>188</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N100" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O100" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>18</v>
@@ -14220,7 +14212,7 @@
         <v>18</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>18</v>
@@ -14235,14 +14227,14 @@
         <v>18</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y100" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y100" t="s" s="2">
+      <c r="Z100" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z100" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA100" t="s" s="2">
         <v>18</v>
       </c>
@@ -14259,7 +14251,7 @@
         <v>18</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>90</v>
@@ -14277,16 +14269,16 @@
         <v>18</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN100" t="s" s="2">
+      <c r="AO100" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>18</v>
@@ -14294,10 +14286,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14320,19 +14312,19 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M101" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O101" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>18</v>
@@ -14381,7 +14373,7 @@
         <v>18</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14399,27 +14391,27 @@
         <v>18</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14445,16 +14437,16 @@
         <v>188</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N102" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O102" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>18</v>
@@ -14479,14 +14471,14 @@
         <v>18</v>
       </c>
       <c r="X102" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y102" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y102" t="s" s="2">
+      <c r="Z102" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z102" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA102" t="s" s="2">
         <v>18</v>
       </c>
@@ -14503,7 +14495,7 @@
         <v>18</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14512,7 +14504,7 @@
         <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
@@ -14527,7 +14519,7 @@
         <v>133</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>18</v>
@@ -14538,14 +14530,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14567,16 +14559,16 @@
         <v>188</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>18</v>
@@ -14601,14 +14593,14 @@
         <v>18</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z103" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA103" t="s" s="2">
         <v>18</v>
       </c>
@@ -14625,7 +14617,7 @@
         <v>18</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14643,27 +14635,27 @@
         <v>18</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP103" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14689,16 +14681,16 @@
         <v>80</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N104" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>18</v>
@@ -14747,7 +14739,7 @@
         <v>18</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14768,10 +14760,10 @@
         <v>18</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>18</v>
@@ -14782,13 +14774,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>18</v>
@@ -14810,19 +14802,19 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>18</v>
@@ -14871,7 +14863,7 @@
         <v>18</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14892,10 +14884,10 @@
         <v>18</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>18</v>
@@ -14906,10 +14898,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14932,13 +14924,13 @@
         <v>18</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14989,7 +14981,7 @@
         <v>18</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15013,7 +15005,7 @@
         <v>18</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>18</v>
@@ -15024,10 +15016,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15056,7 +15048,7 @@
         <v>137</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>139</v>
@@ -15109,7 +15101,7 @@
         <v>18</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15133,7 +15125,7 @@
         <v>18</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>18</v>
@@ -15144,14 +15136,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15173,10 +15165,10 @@
         <v>136</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>139</v>
@@ -15231,7 +15223,7 @@
         <v>18</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15266,10 +15258,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15295,16 +15287,16 @@
         <v>188</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N109" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O109" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>18</v>
@@ -15314,7 +15306,7 @@
         <v>18</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>18</v>
@@ -15329,14 +15321,14 @@
         <v>18</v>
       </c>
       <c r="X109" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y109" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y109" t="s" s="2">
+      <c r="Z109" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>18</v>
       </c>
@@ -15353,7 +15345,7 @@
         <v>18</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>90</v>
@@ -15371,16 +15363,16 @@
         <v>18</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM109" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN109" t="s" s="2">
+      <c r="AO109" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>18</v>
@@ -15388,10 +15380,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15414,19 +15406,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M110" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O110" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>18</v>
@@ -15475,7 +15467,7 @@
         <v>18</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15493,27 +15485,27 @@
         <v>18</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM110" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN110" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN110" t="s" s="2">
+      <c r="AO110" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP110" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15539,16 +15531,16 @@
         <v>188</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N111" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O111" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>18</v>
@@ -15573,14 +15565,14 @@
         <v>18</v>
       </c>
       <c r="X111" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y111" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y111" t="s" s="2">
+      <c r="Z111" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z111" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA111" t="s" s="2">
         <v>18</v>
       </c>
@@ -15597,7 +15589,7 @@
         <v>18</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15606,7 +15598,7 @@
         <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>102</v>
@@ -15621,7 +15613,7 @@
         <v>133</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>18</v>
@@ -15632,14 +15624,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15661,16 +15653,16 @@
         <v>188</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>18</v>
@@ -15695,14 +15687,14 @@
         <v>18</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y112" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z112" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z112" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA112" t="s" s="2">
         <v>18</v>
       </c>
@@ -15719,7 +15711,7 @@
         <v>18</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15737,27 +15729,27 @@
         <v>18</v>
       </c>
       <c r="AL112" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM112" t="s" s="2">
+      <c r="AN112" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN112" t="s" s="2">
+      <c r="AO112" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP112" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15783,16 +15775,16 @@
         <v>80</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M113" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N113" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O113" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>18</v>
@@ -15841,7 +15833,7 @@
         <v>18</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15862,10 +15854,10 @@
         <v>18</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abbey-pain-scale.xlsx
+++ b/StructureDefinition-onc-abbey-pain-scale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
